--- a/Smart Asset Lab.xlsx
+++ b/Smart Asset Lab.xlsx
@@ -501,10 +501,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -521,18 +519,14 @@
           <t>100-ZFA01-7110-003-662</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="E2" t="n">
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13000.0</t>
-        </is>
+      <c r="I2" t="n">
+        <v>13000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -17682,7 +17676,7 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>57000</v>
+        <v>570000</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
